--- a/data/trans_dic/P1427-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1427-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,65</t>
+          <t>3,63; 6,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,84</t>
+          <t>1,67; 4,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 13,61</t>
+          <t>8,23; 12,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,7</t>
+          <t>4,95; 7,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,39</t>
+          <t>4,2; 7,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,57</t>
+          <t>11,75; 15,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,8</t>
+          <t>4,69; 6,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,34</t>
+          <t>3,42; 5,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 14,56</t>
+          <t>10,75; 13,46</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,35</t>
+          <t>0,43; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,96</t>
+          <t>0,3; 1,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,2</t>
+          <t>1,35; 2,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,18</t>
+          <t>0,24; 1,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,48</t>
+          <t>0,56; 1,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,15</t>
+          <t>1,47; 2,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,05</t>
+          <t>0,43; 1,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,05</t>
+          <t>0,49; 1,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,15</t>
+          <t>1,52; 2,17</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,75</t>
+          <t>0,19; 1,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,58</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,52</t>
+          <t>0,88; 2,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,44</t>
+          <t>0,39; 2,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,46</t>
+          <t>1,34; 3,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,24</t>
+          <t>0,2; 1,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,66</t>
+          <t>0,44; 1,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,54</t>
+          <t>1,29; 2,54</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,56</t>
+          <t>1,54; 2,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,47</t>
+          <t>0,77; 1,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,67</t>
+          <t>2,69; 3,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,25</t>
+          <t>2,17; 3,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,81</t>
+          <t>1,8; 2,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,01</t>
+          <t>3,93; 5,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,69</t>
+          <t>1,96; 2,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,03</t>
+          <t>1,4; 2,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,17</t>
+          <t>3,44; 4,15</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57465</t>
+          <t>59048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>106046</t>
+          <t>109408</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>163510</t>
+          <t>168456</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36062; 64854</t>
+          <t>35393; 65393</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12582; 28939</t>
+          <t>12563; 30271</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47054; 69825</t>
+          <t>47431; 70787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66404; 102955</t>
+          <t>66210; 101499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41781; 73554</t>
+          <t>41810; 73165</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92236; 124700</t>
+          <t>96466; 124316</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>110971; 157281</t>
+          <t>108544; 157898</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58881; 93372</t>
+          <t>59741; 95236</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>145065; 184280</t>
+          <t>150201; 188164</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37728</t>
+          <t>40020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>75398</t>
+          <t>80614</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8492; 26593</t>
+          <t>8457; 26112</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6315; 19899</t>
+          <t>6278; 21241</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25633; 50427</t>
+          <t>30020; 51946</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3829; 20701</t>
+          <t>4281; 21204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10890; 29409</t>
+          <t>11063; 29701</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26349; 48100</t>
+          <t>31903; 51202</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16086; 39158</t>
+          <t>16057; 40935</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20381; 42866</t>
+          <t>19990; 43569</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59883; 97473</t>
+          <t>66897; 95595</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>25976</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>917; 8430</t>
+          <t>918; 9434</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>954; 8656</t>
+          <t>979; 9632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5963; 16284</t>
+          <t>6288; 17636</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6998</t>
+          <t>0; 6891</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2105; 13415</t>
+          <t>2141; 14703</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8213; 22818</t>
+          <t>9826; 24644</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1871; 11630</t>
+          <t>1900; 10697</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4901; 18168</t>
+          <t>4783; 18975</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16344; 33190</t>
+          <t>18603; 36703</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>275046</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52997; 87686</t>
+          <t>52712; 88077</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26354; 49736</t>
+          <t>26132; 49195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80658; 126433</t>
+          <t>94401; 127090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76146; 115294</t>
+          <t>77112; 115695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62912; 99155</t>
+          <t>63467; 99736</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>130615; 182851</t>
+          <t>146195; 186297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>137805; 187707</t>
+          <t>136828; 188434</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95102; 140188</t>
+          <t>96807; 139907</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>223484; 295663</t>
+          <t>248700; 300790</t>
         </is>
       </c>
     </row>
